--- a/data/corpus/contacts_oncall.xlsx
+++ b/data/corpus/contacts_oncall.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Yukti Refinery – Contacts   [SYNTHETIC – SIH DEMO]</t>
+          <t>Example Plant – Contacts   [EXAMPLE – prepared by Team UniMinds – NOT MRPL DATA]</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Yukti Refinery – OnCall_2026-09-28   [SYNTHETIC – SIH DEMO]</t>
+          <t>Example Plant – OnCall_2026-09-28   [EXAMPLE – prepared by Team UniMinds – NOT MRPL DATA]</t>
         </is>
       </c>
     </row>
